--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_070_Bosnia_Herzegovina.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_070_Bosnia_Herzegovina.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rbd70eab7c376449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd2578c98c1314d42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfbef6b538fe74a20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R290ce6692ba24533"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb6e62a9f37d747a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rab7a7d54f4624794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra6b566eeacec45f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc6dad65b2cd2455e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R54887d0e1ce14000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1d8c625d6caf4316"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R908bb43910584455"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R78b68ccb129d481c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ070CommercialTable" displayName="EEZ070CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ070CommercialTable" displayName="EEZ070CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ070FunctionalTable" displayName="EEZ070FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ070FunctionalTable" displayName="EEZ070FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ070ValidationTable" displayName="EEZ070ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ070ValidationTable" displayName="EEZ070ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3709,7 +3663,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dbe153d09a04f79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R037f398fdafa4c29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3719,20 +3673,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3740,606 +3684,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6.278275087</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1979501543430864</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>157.74302115445678</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6.278275087</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>157.81368182535644</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$46,A2,'Species'!$U$2:$U$46))</x:f>
-        <x:v>990.7977069918801</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1979501543430864</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>157.74302115445678</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>990.35407986214</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0.44362712974009355</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0004479480003776</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0004479480003776504</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.35611281799999994</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.90111195607118</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>79.63646175035365</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.35611281799999994</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>85.23885285979273</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$46,A3,'Species'!$U$2:$U$46))</x:f>
-        <x:v>30.354648094988143</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.90111195607118</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>79.63646175035365</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>28.359564809467646</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1.9950832855204972</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0703495733776018</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.07034957337760177</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.22387113300000003</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2141512355235187</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>163.73866136588535</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.22387113300000003</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>176.42718569086227</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$46,A4,'Species'!$U$2:$U$46))</x:f>
-        <x:v>39.49695395261473</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2141512355235187</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>163.73866136588535</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>36.65635963588409</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2.8405943167306447</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0774925373099487</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.07749253730994869</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>42.205026589</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.1461757839448428</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>140.01539306874176</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>42.205026589</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>140.49206639238125</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$46,A5,'Species'!$U$2:$U$46))</x:f>
-        <x:v>5929.471397634004</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.1461757839448428</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>140.01539306874176</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5909.353387335532</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>20.118010298471745</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0034044351352531</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.003404435135253056</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.094984194</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.094984194</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941673</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$46,A6,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1.1957801554538707</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>1.1957801554538707</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>8.381166937</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3601201604427606</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>229.1501576907915</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>8.381166937</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>264.289547225271</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$46,A7,'Species'!$U$2:$U$46))</x:f>
-        <x:v>2215.0548149991414</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3601201604427606</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>229.1501576907915</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1920.545725246398</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>294.5090897527434</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1533465649275074</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.15334656492750734</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>2.8397357519999997</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6612665458740197</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>458.4231551080772</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>2.8397357519999997</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>804.9995775371606</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$46,A8,'Species'!$U$2:$U$46))</x:f>
-        <x:v>2285.986080677171</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6612665458740197</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>458.4231551080772</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1301.800623105048</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>984.1854575721227</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.7560185792695726</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7560185792695725</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.057494260000000005</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.057494260000000005</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$46,A9,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>47.82164251435745</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>47.82164251435745</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.11778040099999998</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8855718512114765</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>768.3725674327959</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.11778040099999998</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1116.6126329984943</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$46,A10,'Species'!$U$2:$U$46))</x:f>
-        <x:v>131.51508367622847</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8855718512114765</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>768.3725674327959</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>90.49922910963423</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>41.01585456659424</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.453217723179786</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.4532177231797861</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.466110122</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.447932553136017</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2804.99798192411</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.466110122</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2814.120547564521</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$46,A11,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1311.6900717480057</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.447932553136017</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2804.99798192411</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1307.4379515644007</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4.2521201836050295</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0032522539050646</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0032522539050646353</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ec6f78398494e2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R976d93871e164289"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4349,20 +3899,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4370,930 +3910,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1.195935897</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.808223824458043</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>643.0190277769087</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1.195935897</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>646.1922925844636</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$46,A2,'Species'!$U$2:$U$46))</x:f>
-        <x:v>772.8045590664871</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.808223824458043</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>643.0190277769087</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>769.0095377724452</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3.795021294041817</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0049349469774258</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0049349469774259</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.056299722</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.1663803798178614</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>146.6832013435746</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.056299722</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1463.0347813548988</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$46,A3,'Species'!$U$2:$U$46))</x:f>
-        <x:v>82.36845146661159</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.1663803798178614</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>146.6832013435746</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8.258223457713278</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>74.1102280088983</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>9.974112699708856</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>8.974112699708856</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.037302886</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.218518515162606</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1653.9352950574246</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.037302886</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1791.0183436818124</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$46,A4,'Species'!$U$2:$U$46))</x:f>
-        <x:v>66.81015309827147</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.218518515162606</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1653.9352950574246</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>61.696559762903476</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>5.1135933353679945</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0828829574131726</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08288295741317273</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.420863105</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.4502297924404655</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2819.874579186612</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.420863105</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2819.945017195835</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$46,A5,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1186.8108158663176</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.4502297924404655</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2819.874579186612</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1186.781171107046</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0.029644759271604926</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000249791284133</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.000024979128413329882</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.046628604</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>229.08676527677724</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.046628604</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$46,A6,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>10.681996059731796</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>229.08676527677724</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>10.681996059731796</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.06232981800000001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.9649964997491245</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>922.5639916045386</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.06232981800000001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1012.5654394210799</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$46,A7,'Species'!$U$2:$U$46))</x:f>
-        <x:v>63.11301955220594</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.9649964997491245</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>922.5639916045386</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>57.503245690064425</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>5.609773862141516</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0975557778490892</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.09755577784908911</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.07115179699999999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.23</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1698.243652461746</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.07115179699999999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1698.243652461746</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$46,A8,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>120.83308761649668</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.23</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1698.243652461746</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>120.83308761649668</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.35611281799999994</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.90111195607118</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>79.63646175035365</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.35611281799999994</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>85.23885285979273</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$46,A9,'Species'!$U$2:$U$46))</x:f>
-        <x:v>30.354648094988143</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.90111195607118</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>79.63646175035365</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>28.359564809467646</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1.9950832855204972</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0703495733776018</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.07034957337760177</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>0.31071228900000003</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.138964624987845</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>137.70972942759954</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>0.31071228900000003</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>179.09314424745756</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$46,A10,'Species'!$U$2:$U$46))</x:f>
-        <x:v>55.646440793334726</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.138964624987845</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>137.70972942759954</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>42.788105248020116</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>12.85833554531461</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3005119172906023</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.30051191729060234</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>7.308890175999999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.2728651205621837</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>187.44122788467268</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>7.308890175999999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>188.77610816984836</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$46,A11,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1379.743842466118</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.2728651205621837</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>187.44122788467268</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1369.9873490636612</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>9.756493402456726</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0071215937936397</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.007121593793639738</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1.3367323759999998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.135352344319967</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1365.6906758935934</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1.3367323759999998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1487.3491260031115</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$46,A12,'Species'!$U$2:$U$46))</x:f>
-        <x:v>1988.1877311436624</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.135352344319967</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1365.6906758935934</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1825.5629420682887</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>162.62478907537366</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0890819951083837</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.08908199510838359</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.9429074180000001</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.3770634704562266</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>238.2667661563723</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.9429074180000001</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>265.7054077752564</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$46,A13,'Species'!$U$2:$U$46))</x:f>
-        <x:v>250.53559999400417</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.3770634704562266</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>238.2667661563723</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>224.66350127171484</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>25.872098722289337</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.115159331960196</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.11515933196019605</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>0.094984194</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>0.094984194</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>12.589254117941673</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$46,A14,'Species'!$U$2:$U$46))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1.1957801554538707</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>1.1957801554538707</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>0.037302883</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3800000000000003</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>239.88329190194924</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>0.037302883</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>239.88329190194895</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$46,A15,'Species'!$U$2:$U$46))</x:f>
-        <x:v>8.94833837147325</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3800000000000003</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>239.88329190194924</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8.94833837147326</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>-1.0658141036401503e-14</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>-1.1910748782566142e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>48.518532177</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.1529144460445373</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>142.20486226864855</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>48.518532177</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>142.74654347497437</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$46,A16,'Species'!$U$2:$U$46))</x:f>
-        <x:v>6925.8527627460735</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.1529144460445373</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>142.20486226864855</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>6899.571185707277</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>26.28157703879606</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.003809160936442</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.0038091609364418674</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>0.22387113300000003</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2141512355235187</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>163.73866136588535</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>0.22387113300000003</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>176.42718569086227</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$46,A17,'Species'!$U$2:$U$46))</x:f>
-        <x:v>39.49695395261473</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2141512355235187</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>163.73866136588535</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>36.65635963588409</x:v>
       </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2.8405943167306447</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0774925373099487</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.07749253730994869</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59090e35ec3242b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99499d5fc09848e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5468,7 +4404,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5567,7 +4503,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>12983.384180443843</x:v>
+        <x:v>11634.024343338317</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5581,7 +4517,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>12983.384180443845</x:v>
+        <x:v>12652.496947797641</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5595,7 +4531,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-3.637978807091713e-12</x:v>
+        <x:v>-1349.3598371055305</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5609,7 +4545,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.8189894035458565e-12</x:v>
+        <x:v>-330.88723264620603</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5620,9 +4556,9 @@
         <x:v>EEZ_070</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5634,47 +4570,19 @@
         <x:v>EEZ_070</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_070</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_070</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcca18bdde25c4ebe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb5f60451b4447c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5721,7 +4629,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
